--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92950</v>
+        <v>92951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136858044</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92951</v>
+        <v>92957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92957</v>
+        <v>92961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136858044</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92961</v>
+        <v>92963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136858044</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92963</v>
+        <v>92976</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136858044</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92976</v>
+        <v>92978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136858044</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92978</v>
+        <v>92981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92981</v>
+        <v>92991</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136858044</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92991</v>
+        <v>92992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92992</v>
+        <v>92995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136858044</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92995</v>
+        <v>92997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>92997</v>
+        <v>93003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136858044</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41275-2026 artfynd.xlsx
+++ b/artfynd/A 41275-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136857993</v>
       </c>
       <c r="B2" t="n">
-        <v>93003</v>
+        <v>93015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136858044</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
